--- a/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-medium_voc_otx_cut.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-medium_voc_otx_cut.xlsx
@@ -594,53 +594,53 @@
         <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>121.0719428062439</v>
+        <v>121.7937743663788</v>
       </c>
       <c r="D2" t="n">
-        <v>2.859999895095825</v>
+        <v>2.920000076293945</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0569371461336101</v>
+        <v>0.0575882781829152</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8584654331207275</v>
+        <v>0.8589034080505371</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8584654331207275</v>
+        <v>0.8589034080505371</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8572751879692078</v>
+        <v>0.8570287227630615</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8576263189315796</v>
+        <v>0.8548480868339539</v>
       </c>
       <c r="J2" t="n">
-        <v>0.047681163996458</v>
+        <v>0.0494686104357242</v>
       </c>
       <c r="K2" t="n">
-        <v>116.1139075756073</v>
+        <v>117.694658279419</v>
       </c>
       <c r="L2" t="n">
-        <v>2.802636623382568</v>
+        <v>2.831365823745728</v>
       </c>
       <c r="M2" t="n">
-        <v>32.99549031257629</v>
+        <v>34.43973994255066</v>
       </c>
       <c r="N2" t="n">
-        <v>27.32535457611084</v>
+        <v>27.05940651893616</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0093421220779418</v>
+        <v>0.009437886079152399</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1099849677085876</v>
+        <v>0.1147991331418355</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0910845152537028</v>
+        <v>0.0901980217297871</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-124050</t>
+          <t>20250720-052515</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -665,22 +665,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -690,10 +690,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -712,56 +712,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>113.0249743461609</v>
+        <v>194.6314074993133</v>
       </c>
       <c r="D3" t="n">
-        <v>2.839999914169312</v>
+        <v>2.970000028610229</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0570827905948345</v>
+        <v>0.0573837272822856</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8608587980270386</v>
+        <v>0.8664580583572388</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8608587980270386</v>
+        <v>0.8664580583572388</v>
       </c>
       <c r="H3" t="n">
-        <v>0.858979344367981</v>
+        <v>0.8648409247398376</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8591160178184509</v>
+        <v>0.8655320405960083</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0504051893949508</v>
+        <v>0.0486292466521263</v>
       </c>
       <c r="K3" t="n">
-        <v>115.9952845573425</v>
+        <v>97.38388538360596</v>
       </c>
       <c r="L3" t="n">
-        <v>2.918322801589966</v>
+        <v>2.870413780212402</v>
       </c>
       <c r="M3" t="n">
-        <v>34.14213752746582</v>
+        <v>34.6543116569519</v>
       </c>
       <c r="N3" t="n">
-        <v>27.41137433052063</v>
+        <v>27.14556813240052</v>
       </c>
       <c r="O3" t="n">
-        <v>0.009727742671966501</v>
+        <v>0.0095680459340413</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1138071250915527</v>
+        <v>0.1155143721898396</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.09137124776840209</v>
+        <v>0.09048522710800171</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-124650</t>
+          <t>20250720-053120</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -786,22 +786,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -811,10 +811,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -833,56 +833,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>112.7915995121002</v>
+        <v>227.1069238185882</v>
       </c>
       <c r="D4" t="n">
-        <v>3.349999904632568</v>
+        <v>3.019999980926514</v>
       </c>
       <c r="E4" t="n">
-        <v>0.057048972409505</v>
+        <v>0.057619768988203</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8621517419815063</v>
+        <v>0.8670738339424133</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8621517419815063</v>
+        <v>0.8670738339424133</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8602656126022339</v>
+        <v>0.8653272390365601</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8589689135551453</v>
+        <v>0.8652161955833435</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0478978268802166</v>
+        <v>0.0490317530930042</v>
       </c>
       <c r="K4" t="n">
-        <v>115.4281125068665</v>
+        <v>98.21344399452209</v>
       </c>
       <c r="L4" t="n">
-        <v>2.792884826660156</v>
+        <v>2.844554901123047</v>
       </c>
       <c r="M4" t="n">
-        <v>33.84742569923401</v>
+        <v>35.51193261146545</v>
       </c>
       <c r="N4" t="n">
-        <v>27.85785627365112</v>
+        <v>27.67986178398132</v>
       </c>
       <c r="O4" t="n">
-        <v>0.009309616088867099</v>
+        <v>0.009481849670410099</v>
       </c>
       <c r="P4" t="n">
-        <v>0.11282475233078</v>
+        <v>0.1183731087048848</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0928595209121704</v>
+        <v>0.0922662059466044</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-125243</t>
+          <t>20250720-053839</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -907,22 +907,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -932,10 +932,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -954,56 +954,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>112.7787992954254</v>
+        <v>187.218635559082</v>
       </c>
       <c r="D5" t="n">
-        <v>3.269999980926514</v>
+        <v>2.950000047683716</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0572357727931095</v>
+        <v>0.0575863226232203</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8573452234268188</v>
+        <v>0.8691561222076416</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8573452234268188</v>
+        <v>0.8691561222076416</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8544898629188538</v>
+        <v>0.8684744238853455</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8533482551574707</v>
+        <v>0.8685203790664673</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0471766851842403</v>
+        <v>0.0481590740382671</v>
       </c>
       <c r="K5" t="n">
-        <v>114.9449353218079</v>
+        <v>119.0388715267181</v>
       </c>
       <c r="L5" t="n">
-        <v>2.783872127532959</v>
+        <v>2.879686832427979</v>
       </c>
       <c r="M5" t="n">
-        <v>33.52969360351562</v>
+        <v>34.99031782150269</v>
       </c>
       <c r="N5" t="n">
-        <v>27.10711073875427</v>
+        <v>27.76391911506653</v>
       </c>
       <c r="O5" t="n">
-        <v>0.009279573758443099</v>
+        <v>0.0095989561080932</v>
       </c>
       <c r="P5" t="n">
-        <v>0.111765645345052</v>
+        <v>0.1166343927383422</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0903570357958475</v>
+        <v>0.0925463970502217</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-125836</t>
+          <t>20250720-054612</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1028,22 +1028,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1053,10 +1053,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1075,56 +1075,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>114.1151440143585</v>
+        <v>154.6058716773987</v>
       </c>
       <c r="D6" t="n">
-        <v>2.700000047683716</v>
+        <v>3.450000047683716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.057577456992406</v>
+        <v>0.0578741418818632</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8556059598922729</v>
+        <v>0.8706749677658081</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8556059598922729</v>
+        <v>0.8706749677658081</v>
       </c>
       <c r="H6" t="n">
-        <v>0.855253279209137</v>
+        <v>0.8690341114997864</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8549959063529968</v>
+        <v>0.8683939576148987</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0486077070236206</v>
+        <v>0.050305601209402</v>
       </c>
       <c r="K6" t="n">
-        <v>116.950868844986</v>
+        <v>119.278862953186</v>
       </c>
       <c r="L6" t="n">
-        <v>2.900665760040283</v>
+        <v>2.91360092163086</v>
       </c>
       <c r="M6" t="n">
-        <v>34.25914072990417</v>
+        <v>34.81811738014221</v>
       </c>
       <c r="N6" t="n">
-        <v>30.89646005630493</v>
+        <v>28.27347469329834</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0096688858668009</v>
+        <v>0.0097120030721028</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1141971357663472</v>
+        <v>0.1160603912671407</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1029882001876831</v>
+        <v>0.0942449156443278</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-130426</t>
+          <t>20250720-055325</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1174,10 +1174,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1362,56 +1362,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C2" t="n">
-        <v>226.2619154453278</v>
+        <v>1040.669723272324</v>
       </c>
       <c r="D2" t="n">
-        <v>3.470000028610229</v>
+        <v>3.589999914169312</v>
       </c>
       <c r="E2" t="n">
-        <v>0.154881818840901</v>
+        <v>0.1592870262162438</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2342186123132705</v>
+        <v>0.4335594773292541</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2342186123132705</v>
+        <v>0.4335594773292541</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2341296672821045</v>
+        <v>0.4325537383556366</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2185081243515014</v>
+        <v>0.4118233323097229</v>
       </c>
       <c r="J2" t="n">
-        <v>0.07448806613683701</v>
+        <v>0.0785726308822631</v>
       </c>
       <c r="K2" t="n">
-        <v>270.2448282241821</v>
+        <v>280.1349849700928</v>
       </c>
       <c r="L2" t="n">
-        <v>4.031704425811768</v>
+        <v>4.292927026748657</v>
       </c>
       <c r="M2" t="n">
-        <v>26.09730792045593</v>
+        <v>27.16703820228577</v>
       </c>
       <c r="N2" t="n">
-        <v>28.22692894935608</v>
+        <v>29.57709670066833</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0134390147527058</v>
+        <v>0.0143097567558288</v>
       </c>
       <c r="P2" t="n">
-        <v>0.08699102640151971</v>
+        <v>0.09055679400761921</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0940897631645202</v>
+        <v>0.0985903223355611</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-130612</t>
+          <t>20250718-094348</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1436,22 +1436,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1461,10 +1461,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1483,56 +1483,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C3" t="n">
-        <v>227.2598259449005</v>
+        <v>994.8900792598724</v>
       </c>
       <c r="D3" t="n">
-        <v>3.329999923706055</v>
+        <v>3.380000114440918</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1542949378490447</v>
+        <v>0.158396285825542</v>
       </c>
       <c r="F3" t="n">
-        <v>0.237453818321228</v>
+        <v>0.4611483812332153</v>
       </c>
       <c r="G3" t="n">
-        <v>0.237453818321228</v>
+        <v>0.4611483812332153</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2370980679988861</v>
+        <v>0.4577746987342834</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2308557331562042</v>
+        <v>0.4215841591358185</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0775044783949852</v>
+        <v>0.0766185745596885</v>
       </c>
       <c r="K3" t="n">
-        <v>278.9036567211151</v>
+        <v>280.218624830246</v>
       </c>
       <c r="L3" t="n">
-        <v>4.415918588638306</v>
+        <v>4.499752759933472</v>
       </c>
       <c r="M3" t="n">
-        <v>25.88737058639526</v>
+        <v>26.80859589576721</v>
       </c>
       <c r="N3" t="n">
-        <v>28.46637153625488</v>
+        <v>29.64814186096192</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0147197286287943</v>
+        <v>0.0149991758664449</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0862912352879842</v>
+        <v>0.089361986319224</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0948879051208496</v>
+        <v>0.0988271395365397</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-131621</t>
+          <t>20250718-100746</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1557,22 +1557,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1582,10 +1582,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1604,56 +1604,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="C4" t="n">
-        <v>228.3010473251343</v>
+        <v>1182.078561067581</v>
       </c>
       <c r="D4" t="n">
-        <v>3.329999923706055</v>
+        <v>3.589999914169312</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1560234750310579</v>
+        <v>0.1600712727416645</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2186202257871627</v>
+        <v>0.4409859180450439</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2186202257871627</v>
+        <v>0.4409859180450439</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2183030694723129</v>
+        <v>0.4374566674232483</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2155994772911071</v>
+        <v>0.4218841791152954</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07408808916807171</v>
+        <v>0.0774475261569023</v>
       </c>
       <c r="K4" t="n">
-        <v>279.0415263175964</v>
+        <v>278.1540446281433</v>
       </c>
       <c r="L4" t="n">
-        <v>4.393590211868286</v>
+        <v>4.21699857711792</v>
       </c>
       <c r="M4" t="n">
-        <v>27.27827978134156</v>
+        <v>27.28056406974792</v>
       </c>
       <c r="N4" t="n">
-        <v>28.02285957336425</v>
+        <v>30.48619985580444</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0146453007062276</v>
+        <v>0.0140566619237263</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0909275992711385</v>
+        <v>0.0909352135658264</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.09340953191121409</v>
+        <v>0.1016206661860148</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-132639</t>
+          <t>20250718-103059</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1678,22 +1678,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1703,10 +1703,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1725,56 +1725,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>244.1132295131684</v>
+        <v>872.3858640193939</v>
       </c>
       <c r="D5" t="n">
-        <v>3.329999923706055</v>
+        <v>3.650000095367432</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1547321585508493</v>
+        <v>0.1618231566001971</v>
       </c>
       <c r="F5" t="n">
-        <v>0.241916686296463</v>
+        <v>0.4513498246669769</v>
       </c>
       <c r="G5" t="n">
-        <v>0.241916686296463</v>
+        <v>0.4513498246669769</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2406005710363388</v>
+        <v>0.4452738165855407</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2286795973777771</v>
+        <v>0.4067710936069488</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0768559724092483</v>
+        <v>0.0791566595435142</v>
       </c>
       <c r="K5" t="n">
-        <v>269.0581152439117</v>
+        <v>278.1097288131714</v>
       </c>
       <c r="L5" t="n">
-        <v>4.142680406570435</v>
+        <v>4.294839859008789</v>
       </c>
       <c r="M5" t="n">
-        <v>26.67520022392273</v>
+        <v>28.07421898841858</v>
       </c>
       <c r="N5" t="n">
-        <v>28.65758752822876</v>
+        <v>29.225266456604</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0138089346885681</v>
+        <v>0.0143161328633626</v>
       </c>
       <c r="P5" t="n">
-        <v>0.08891733407974239</v>
+        <v>0.0935807299613952</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.09552529176076251</v>
+        <v>0.0974175548553466</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-133721</t>
+          <t>20250718-105717</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1799,22 +1799,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1824,10 +1824,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1846,56 +1846,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="C6" t="n">
-        <v>227.1040534973145</v>
+        <v>1506.020116090774</v>
       </c>
       <c r="D6" t="n">
-        <v>3.220000028610229</v>
+        <v>3.599999904632568</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1541802287101745</v>
+        <v>0.1588170593275742</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2316907048225402</v>
+        <v>0.4874013066291809</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2316907048225402</v>
+        <v>0.4874013066291809</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2303031384944915</v>
+        <v>0.4866408407688141</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2229342460632324</v>
+        <v>0.456002414226532</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0712852999567985</v>
+        <v>0.0744615197181701</v>
       </c>
       <c r="K6" t="n">
-        <v>269.4398925304413</v>
+        <v>278.7151334285736</v>
       </c>
       <c r="L6" t="n">
-        <v>4.044149160385132</v>
+        <v>4.096726655960083</v>
       </c>
       <c r="M6" t="n">
-        <v>26.3365569114685</v>
+        <v>27.51107168197632</v>
       </c>
       <c r="N6" t="n">
-        <v>27.95210695266724</v>
+        <v>29.54946756362915</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0134804972012837</v>
+        <v>0.0136557555198669</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0877885230382283</v>
+        <v>0.09170357227325431</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0931736898422241</v>
+        <v>0.0984982252120971</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-134748</t>
+          <t>20250718-111825</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1945,10 +1945,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2133,56 +2133,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="C2" t="n">
-        <v>229.3340635299682</v>
+        <v>983.8640806674956</v>
       </c>
       <c r="D2" t="n">
-        <v>2.009999990463257</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1350137474281447</v>
+        <v>0.1370322586052001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2314652204513549</v>
+        <v>0.4407634735107422</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2314652204513549</v>
+        <v>0.4407634735107422</v>
       </c>
       <c r="H2" t="n">
-        <v>0.230329543352127</v>
+        <v>0.4418756067752838</v>
       </c>
       <c r="I2" t="n">
-        <v>0.150452584028244</v>
+        <v>0.1708790361881256</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0666396990418434</v>
+        <v>0.069662258028984</v>
       </c>
       <c r="K2" t="n">
-        <v>218.1372888088226</v>
+        <v>227.957426071167</v>
       </c>
       <c r="L2" t="n">
-        <v>3.89322829246521</v>
+        <v>4.049444437026978</v>
       </c>
       <c r="M2" t="n">
-        <v>44.381014585495</v>
+        <v>45.03544473648071</v>
       </c>
       <c r="N2" t="n">
-        <v>47.9122531414032</v>
+        <v>48.16569018363953</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0129774276415507</v>
+        <v>0.0134981481234232</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1479367152849833</v>
+        <v>0.1501181491216023</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.159707510471344</v>
+        <v>0.1605523006121317</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-160847</t>
+          <t>20250718-154852</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2207,22 +2207,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -2232,10 +2232,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2254,56 +2254,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="C3" t="n">
-        <v>211.6487829685211</v>
+        <v>1404.234761953354</v>
       </c>
       <c r="D3" t="n">
-        <v>2.289999961853028</v>
+        <v>2.609999895095825</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1333173490487612</v>
+        <v>0.1370013981730073</v>
       </c>
       <c r="F3" t="n">
-        <v>0.228873923420906</v>
+        <v>0.4653962850570678</v>
       </c>
       <c r="G3" t="n">
-        <v>0.228873923420906</v>
+        <v>0.4653962850570678</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2287825942039489</v>
+        <v>0.4664292335510254</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1470243781805038</v>
+        <v>0.1679614931344986</v>
       </c>
       <c r="J3" t="n">
-        <v>0.06584709137678139</v>
+        <v>0.0650599524378776</v>
       </c>
       <c r="K3" t="n">
-        <v>219.6369898319244</v>
+        <v>226.4614882469177</v>
       </c>
       <c r="L3" t="n">
-        <v>3.66718602180481</v>
+        <v>3.633116960525513</v>
       </c>
       <c r="M3" t="n">
-        <v>44.8130464553833</v>
+        <v>45.14480781555176</v>
       </c>
       <c r="N3" t="n">
-        <v>48.46229839324951</v>
+        <v>50.83521151542664</v>
       </c>
       <c r="O3" t="n">
-        <v>0.012223953406016</v>
+        <v>0.0121103898684183</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1493768215179443</v>
+        <v>0.1504826927185058</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.161540994644165</v>
+        <v>0.1694507050514221</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-161844</t>
+          <t>20250718-161136</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -2328,22 +2328,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -2353,10 +2353,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2375,56 +2375,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="C4" t="n">
-        <v>213.6761124134064</v>
+        <v>1158.33188700676</v>
       </c>
       <c r="D4" t="n">
-        <v>2.190000057220459</v>
+        <v>2.380000114440918</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1345628740695806</v>
+        <v>0.1382459126211501</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2252774536609649</v>
+        <v>0.4294037818908691</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2252774536609649</v>
+        <v>0.4294037818908691</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2239696085453033</v>
+        <v>0.4253938496112823</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1830160766839981</v>
+        <v>0.2248849272727966</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0617063380777835</v>
+        <v>0.0698926970362663</v>
       </c>
       <c r="K4" t="n">
-        <v>218.0023295879364</v>
+        <v>227.8195104598999</v>
       </c>
       <c r="L4" t="n">
-        <v>3.451472282409668</v>
+        <v>3.762341976165772</v>
       </c>
       <c r="M4" t="n">
-        <v>44.68827342987061</v>
+        <v>45.05702161788941</v>
       </c>
       <c r="N4" t="n">
-        <v>49.38483715057373</v>
+        <v>49.30502653121948</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0115049076080322</v>
+        <v>0.0125411399205525</v>
       </c>
       <c r="P4" t="n">
-        <v>0.148960911432902</v>
+        <v>0.1501900720596313</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1646161238352457</v>
+        <v>0.1643500884373982</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-162825</t>
+          <t>20250718-164122</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -2474,10 +2474,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2496,56 +2496,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="C5" t="n">
-        <v>214.1996386051178</v>
+        <v>954.6415822505952</v>
       </c>
       <c r="D5" t="n">
-        <v>2.279999971389771</v>
+        <v>2.440000057220459</v>
       </c>
       <c r="E5" t="n">
-        <v>0.134754982132178</v>
+        <v>0.1378583524559364</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2086172103881836</v>
+        <v>0.4262373745441437</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2086172103881836</v>
+        <v>0.4262373745441437</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2072609364986419</v>
+        <v>0.4258880615234375</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1067062765359878</v>
+        <v>0.0404067374765872</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0656172186136245</v>
+        <v>0.0723888278007507</v>
       </c>
       <c r="K5" t="n">
-        <v>218.9353108406067</v>
+        <v>227.6127681732178</v>
       </c>
       <c r="L5" t="n">
-        <v>3.562476873397827</v>
+        <v>3.868197679519653</v>
       </c>
       <c r="M5" t="n">
-        <v>43.54470801353455</v>
+        <v>45.18062734603882</v>
       </c>
       <c r="N5" t="n">
-        <v>47.69195365905762</v>
+        <v>48.56514286994934</v>
       </c>
       <c r="O5" t="n">
-        <v>0.011874922911326</v>
+        <v>0.0128939922650655</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1451490267117818</v>
+        <v>0.1506020911534627</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1589731788635253</v>
+        <v>0.1618838095664978</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-163807</t>
+          <t>20250718-170701</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2570,22 +2570,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -2595,10 +2595,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2617,56 +2617,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="C6" t="n">
-        <v>197.4803729057312</v>
+        <v>808.9806344509125</v>
       </c>
       <c r="D6" t="n">
-        <v>2.339999914169312</v>
+        <v>2.380000114440918</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1332112265129883</v>
+        <v>0.1370629413196673</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2056200504302978</v>
+        <v>0.343228131532669</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2056200504302978</v>
+        <v>0.343228131532669</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2051147818565368</v>
+        <v>0.3435681760311126</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1463365256786346</v>
+        <v>0.1790367364883422</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06555136293172829</v>
+        <v>0.06616265326738351</v>
       </c>
       <c r="K6" t="n">
-        <v>218.9005477428436</v>
+        <v>227.2804524898529</v>
       </c>
       <c r="L6" t="n">
-        <v>3.610137701034546</v>
+        <v>3.916424751281737</v>
       </c>
       <c r="M6" t="n">
-        <v>44.81741380691528</v>
+        <v>44.7244553565979</v>
       </c>
       <c r="N6" t="n">
-        <v>47.66305708885193</v>
+        <v>51.17310166358948</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0120337923367818</v>
+        <v>0.0130547491709391</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1493913793563842</v>
+        <v>0.1490815178553263</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1588768569628397</v>
+        <v>0.1705770055452982</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-164748</t>
+          <t>20250718-172937</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2691,22 +2691,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2716,10 +2716,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2904,56 +2904,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="C2" t="n">
-        <v>437.1095612049103</v>
+        <v>2264.355836868286</v>
       </c>
       <c r="D2" t="n">
-        <v>9.479999542236328</v>
+        <v>9.439999580383301</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3301262706518173</v>
+        <v>0.3342647042238351</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1416006684303283</v>
+        <v>0.391095757484436</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1416006684303283</v>
+        <v>0.391095757484436</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1404152363538742</v>
+        <v>0.392266035079956</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0707603320479393</v>
+        <v>0.0747148990631103</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1152870208024978</v>
+        <v>0.1192799359560012</v>
       </c>
       <c r="K2" t="n">
-        <v>1776.822695016861</v>
+        <v>1842.692344427109</v>
       </c>
       <c r="L2" t="n">
-        <v>6.42586612701416</v>
+        <v>6.653113126754761</v>
       </c>
       <c r="M2" t="n">
-        <v>45.59025311470032</v>
+        <v>47.08949375152588</v>
       </c>
       <c r="N2" t="n">
-        <v>48.5515284538269</v>
+        <v>50.8669228553772</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0214195537567138</v>
+        <v>0.0221770437558492</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1519675103823344</v>
+        <v>0.1569649791717529</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.161838428179423</v>
+        <v>0.169556409517924</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-211753</t>
+          <t>20250718-235203</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2978,22 +2978,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3003,10 +3003,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3025,56 +3025,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="C3" t="n">
-        <v>505.2155454158783</v>
+        <v>2422.346768140793</v>
       </c>
       <c r="D3" t="n">
-        <v>9.390000343322754</v>
+        <v>9.449999809265137</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3300577316965375</v>
+        <v>0.3334670650287413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1865429282188415</v>
+        <v>0.3838217556476593</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1865429282188415</v>
+        <v>0.3838217556476593</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1857314556837082</v>
+        <v>0.383714348077774</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0821118056774139</v>
+        <v>0.1070767939090728</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1144337877631187</v>
+        <v>0.115086019039154</v>
       </c>
       <c r="K3" t="n">
-        <v>1792.376763820648</v>
+        <v>1842.184654712677</v>
       </c>
       <c r="L3" t="n">
-        <v>6.491649150848389</v>
+        <v>6.497223138809204</v>
       </c>
       <c r="M3" t="n">
-        <v>45.86509919166565</v>
+        <v>47.6969256401062</v>
       </c>
       <c r="N3" t="n">
-        <v>48.74488973617554</v>
+        <v>50.21492433547974</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0216388305028279</v>
+        <v>0.0216574104626973</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1528836639722188</v>
+        <v>0.1589897521336873</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1624829657872518</v>
+        <v>0.1673830811182657</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-215748</t>
+          <t>20250719-010339</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3099,22 +3099,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3124,10 +3124,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3146,56 +3146,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="C4" t="n">
-        <v>438.9586033821106</v>
+        <v>2732.963873147964</v>
       </c>
       <c r="D4" t="n">
-        <v>9.390000343322754</v>
+        <v>9.5</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3306771765152613</v>
+        <v>0.3343731746077537</v>
       </c>
       <c r="F4" t="n">
-        <v>0.16874960064888</v>
+        <v>0.3699622750282287</v>
       </c>
       <c r="G4" t="n">
-        <v>0.16874960064888</v>
+        <v>0.3699622750282287</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1669619381427765</v>
+        <v>0.3692367374897003</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0608057864010334</v>
+        <v>0.0737020000815391</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1159131377935409</v>
+        <v>0.1200625598430633</v>
       </c>
       <c r="K4" t="n">
-        <v>1777.52426815033</v>
+        <v>1828.769851922989</v>
       </c>
       <c r="L4" t="n">
-        <v>6.503880739212036</v>
+        <v>6.714082717895508</v>
       </c>
       <c r="M4" t="n">
-        <v>45.74164152145386</v>
+        <v>47.23690843582153</v>
       </c>
       <c r="N4" t="n">
-        <v>48.46293950080872</v>
+        <v>50.21334338188171</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0216796024640401</v>
+        <v>0.0223802757263183</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1524721384048462</v>
+        <v>0.1574563614527384</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1615431316693623</v>
+        <v>0.167377811272939</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-223908</t>
+          <t>20250719-021752</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3220,22 +3220,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -3245,10 +3245,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3267,56 +3267,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="C5" t="n">
-        <v>471.8384029865265</v>
+        <v>2056.612390518188</v>
       </c>
       <c r="D5" t="n">
-        <v>9.340000152587891</v>
+        <v>9.449999809265137</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3308928608894348</v>
+        <v>0.3335180694858233</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1468592435121536</v>
+        <v>0.3458226919174194</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1468592435121536</v>
+        <v>0.3458226919174194</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1469175368547439</v>
+        <v>0.3453357219696045</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0550396777689456</v>
+        <v>0.0411288067698478</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1155408322811126</v>
+        <v>0.1172753423452377</v>
       </c>
       <c r="K5" t="n">
-        <v>1771.51512002945</v>
+        <v>1847.139241695404</v>
       </c>
       <c r="L5" t="n">
-        <v>6.516055345535278</v>
+        <v>6.665947198867798</v>
       </c>
       <c r="M5" t="n">
-        <v>45.35021448135376</v>
+        <v>47.25520491600037</v>
       </c>
       <c r="N5" t="n">
-        <v>49.42986726760864</v>
+        <v>49.88571906089783</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0217201844851175</v>
+        <v>0.0222198239962259</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1511673816045125</v>
+        <v>0.1575173497200012</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1647662242253621</v>
+        <v>0.1662857302029927</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-231906</t>
+          <t>20250719-033702</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3341,22 +3341,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -3366,10 +3366,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3388,56 +3388,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="C6" t="n">
-        <v>472.0270488262177</v>
+        <v>2128.156713962555</v>
       </c>
       <c r="D6" t="n">
-        <v>9.390000343322754</v>
+        <v>9.449999809265137</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3303779638730563</v>
+        <v>0.3337059487258234</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1704510152339935</v>
+        <v>0.3975653052330017</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1704510152339935</v>
+        <v>0.3975653052330017</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1694304794073104</v>
+        <v>0.3983821868896484</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0893819108605384</v>
+        <v>0.0843257904052734</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1145450845360755</v>
+        <v>0.1180085018277168</v>
       </c>
       <c r="K6" t="n">
-        <v>1781.44283914566</v>
+        <v>1850.233253955841</v>
       </c>
       <c r="L6" t="n">
-        <v>6.460403203964233</v>
+        <v>6.627603530883789</v>
       </c>
       <c r="M6" t="n">
-        <v>45.40048336982727</v>
+        <v>46.32812643051148</v>
       </c>
       <c r="N6" t="n">
-        <v>48.33667135238648</v>
+        <v>50.80365109443665</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0215346773465474</v>
+        <v>0.0220920117696126</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1513349445660909</v>
+        <v>0.1544270881017049</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1611222378412882</v>
+        <v>0.1693455036481221</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-235932</t>
+          <t>20250719-044514</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -3462,22 +3462,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3487,10 +3487,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3675,56 +3675,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>295.7550463676453</v>
+        <v>627.3350512981415</v>
       </c>
       <c r="D2" t="n">
-        <v>8.380000114440918</v>
+        <v>8.180000305175781</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2060196921229362</v>
+        <v>0.2051198935067212</v>
       </c>
       <c r="F2" t="n">
-        <v>0.802628755569458</v>
+        <v>0.8353222608566284</v>
       </c>
       <c r="G2" t="n">
-        <v>0.802628755569458</v>
+        <v>0.8353222608566284</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8002161383628845</v>
+        <v>0.8335031270980835</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7908629179000854</v>
+        <v>0.8286496996879578</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0851005762815475</v>
+        <v>0.0851237773895263</v>
       </c>
       <c r="K2" t="n">
-        <v>169.1468484401703</v>
+        <v>146.3149056434631</v>
       </c>
       <c r="L2" t="n">
-        <v>4.833151578903198</v>
+        <v>5.07035756111145</v>
       </c>
       <c r="M2" t="n">
-        <v>37.06810832023621</v>
+        <v>37.74934005737305</v>
       </c>
       <c r="N2" t="n">
-        <v>33.01554608345032</v>
+        <v>32.60042119026184</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0161105052630106</v>
+        <v>0.0169011918703715</v>
       </c>
       <c r="P2" t="n">
-        <v>0.123560361067454</v>
+        <v>0.1258311335245768</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1100518202781677</v>
+        <v>0.1086680706342061</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-055131</t>
+          <t>20250719-142836</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3749,22 +3749,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3774,10 +3774,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3796,56 +3796,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>295.7063050270081</v>
+        <v>604.0075459480286</v>
       </c>
       <c r="D3" t="n">
         <v>8.319999694824219</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2057237513363361</v>
+        <v>0.2047882372370133</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8145384788513184</v>
+        <v>0.8269065618515015</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8145384788513184</v>
+        <v>0.8269065618515015</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8136828541755676</v>
+        <v>0.8234704732894897</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8094767332077026</v>
+        <v>0.8122720718383789</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0849761962890625</v>
+        <v>0.0843094140291214</v>
       </c>
       <c r="K3" t="n">
-        <v>166.5111920833588</v>
+        <v>149.6965687274933</v>
       </c>
       <c r="L3" t="n">
-        <v>4.803423643112183</v>
+        <v>4.792565584182739</v>
       </c>
       <c r="M3" t="n">
-        <v>37.21636509895325</v>
+        <v>37.94105815887451</v>
       </c>
       <c r="N3" t="n">
-        <v>33.67424297332764</v>
+        <v>32.89355826377869</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0160114121437072</v>
+        <v>0.0159752186139424</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1240545503298441</v>
+        <v>0.126470193862915</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1122474765777587</v>
+        <v>0.1096451942125956</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-060120</t>
+          <t>20250719-144337</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3870,22 +3870,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3895,10 +3895,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3917,56 +3917,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>296.2316415309906</v>
+        <v>887.8797624111176</v>
       </c>
       <c r="D4" t="n">
-        <v>8.270000457763672</v>
+        <v>8.380000114440918</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2055600471794605</v>
+        <v>0.2048821250597635</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8232391476631165</v>
+        <v>0.8363301753997803</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8232391476631165</v>
+        <v>0.8363301753997803</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8193325400352478</v>
+        <v>0.8331738710403442</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8025168776512146</v>
+        <v>0.8250128030776978</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0849762484431266</v>
+        <v>0.0849953815340995</v>
       </c>
       <c r="K4" t="n">
-        <v>169.2366919517517</v>
+        <v>145.9779160022736</v>
       </c>
       <c r="L4" t="n">
-        <v>4.879279136657715</v>
+        <v>4.805693864822388</v>
       </c>
       <c r="M4" t="n">
-        <v>37.16110444068909</v>
+        <v>37.61803388595581</v>
       </c>
       <c r="N4" t="n">
-        <v>32.48547172546387</v>
+        <v>34.32653117179871</v>
       </c>
       <c r="O4" t="n">
-        <v>0.016264263788859</v>
+        <v>0.0160189795494079</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1238703481356302</v>
+        <v>0.1253934462865193</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1082849057515462</v>
+        <v>0.1144217705726623</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-061109</t>
+          <t>20250719-145839</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3991,22 +3991,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4016,10 +4016,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4038,56 +4038,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>294.8446745872498</v>
+        <v>537.0742132663727</v>
       </c>
       <c r="D5" t="n">
-        <v>8.220000267028809</v>
+        <v>8.359999656677246</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2061305815974871</v>
+        <v>0.2049970607394757</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8123605251312256</v>
+        <v>0.8184016942977905</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8123605251312256</v>
+        <v>0.8184016942977905</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8102462291717529</v>
+        <v>0.8176806569099426</v>
       </c>
       <c r="I5" t="n">
-        <v>0.796804666519165</v>
+        <v>0.8095337748527527</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0855703130364418</v>
+        <v>0.0843097940087318</v>
       </c>
       <c r="K5" t="n">
-        <v>171.8886947631836</v>
+        <v>147.1088199615479</v>
       </c>
       <c r="L5" t="n">
-        <v>4.820262670516968</v>
+        <v>4.800802946090698</v>
       </c>
       <c r="M5" t="n">
-        <v>36.21015286445618</v>
+        <v>37.53899216651917</v>
       </c>
       <c r="N5" t="n">
-        <v>35.5313184261322</v>
+        <v>32.78650212287903</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0160675422350565</v>
+        <v>0.0160026764869689</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1207005095481872</v>
+        <v>0.1251299738883972</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1184377280871073</v>
+        <v>0.1092883404095967</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-062100</t>
+          <t>20250719-151823</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4112,22 +4112,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4137,10 +4137,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4159,56 +4159,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>296.8313355445862</v>
+        <v>666.9687857627869</v>
       </c>
       <c r="D6" t="n">
-        <v>8.220000267028809</v>
+        <v>8.340000152587891</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2074298920730749</v>
+        <v>0.2045877765992592</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8029738664627075</v>
+        <v>0.8314225077629089</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8029738664627075</v>
+        <v>0.8314225077629089</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7993960380554199</v>
+        <v>0.8289631605148315</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7994334101676941</v>
+        <v>0.8206084966659546</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08428562432527539</v>
+        <v>0.08563999086618421</v>
       </c>
       <c r="K6" t="n">
-        <v>165.7470216751099</v>
+        <v>147.273809671402</v>
       </c>
       <c r="L6" t="n">
-        <v>4.778881549835205</v>
+        <v>4.858999729156494</v>
       </c>
       <c r="M6" t="n">
-        <v>39.39240837097168</v>
+        <v>38.30568194389343</v>
       </c>
       <c r="N6" t="n">
-        <v>39.42739939689636</v>
+        <v>32.85431098937988</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0159296051661173</v>
+        <v>0.0161966657638549</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1313080279032389</v>
+        <v>0.1276856064796447</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1314246646563212</v>
+        <v>0.1095143699645996</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-063055</t>
+          <t>20250719-153215</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4233,22 +4233,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -4258,10 +4258,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4446,56 +4446,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C2" t="n">
-        <v>195.2556567192078</v>
+        <v>679.1374168395996</v>
       </c>
       <c r="D2" t="n">
-        <v>5.559999942779541</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1299884604911009</v>
+        <v>0.1304429299301571</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7376757860183716</v>
+        <v>0.80670565366745</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7376757860183716</v>
+        <v>0.80670565366745</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7352644205093384</v>
+        <v>0.8052331805229187</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7349176406860352</v>
+        <v>0.8051472902297974</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0617877319455146</v>
+        <v>0.0625762715935707</v>
       </c>
       <c r="K2" t="n">
-        <v>106.0968716144562</v>
+        <v>106.254120349884</v>
       </c>
       <c r="L2" t="n">
-        <v>3.44692325592041</v>
+        <v>3.491467237472534</v>
       </c>
       <c r="M2" t="n">
-        <v>28.28807044029236</v>
+        <v>28.22064542770386</v>
       </c>
       <c r="N2" t="n">
-        <v>25.81313252449036</v>
+        <v>25.55138301849365</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0114897441864013</v>
+        <v>0.0116382241249084</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0942935681343078</v>
+        <v>0.0940688180923461</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.08604377508163449</v>
+        <v>0.0851712767283121</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-083641</t>
+          <t>20250719-203656</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4520,22 +4520,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4545,10 +4545,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4567,56 +4567,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="C3" t="n">
-        <v>195.8999426364899</v>
+        <v>626.059424161911</v>
       </c>
       <c r="D3" t="n">
-        <v>5.659999847412109</v>
+        <v>6.369999885559082</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1302351305882136</v>
+        <v>0.1279324090906551</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7427655458450317</v>
+        <v>0.8057955503463745</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7427655458450317</v>
+        <v>0.8057955503463745</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7412599325180054</v>
+        <v>0.8040726780891418</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7364579439163208</v>
+        <v>0.7995801568031311</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0636114254593849</v>
+        <v>0.0635520666837692</v>
       </c>
       <c r="K3" t="n">
-        <v>87.35823678970337</v>
+        <v>86.0214900970459</v>
       </c>
       <c r="L3" t="n">
-        <v>3.504246473312378</v>
+        <v>3.516921758651733</v>
       </c>
       <c r="M3" t="n">
-        <v>27.82910966873169</v>
+        <v>28.65989637374878</v>
       </c>
       <c r="N3" t="n">
-        <v>25.33183622360229</v>
+        <v>27.43337202072144</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0116808215777079</v>
+        <v>0.0117230725288391</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0927636988957723</v>
+        <v>0.0955329879124959</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0844394540786743</v>
+        <v>0.09144457340240469</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-084322</t>
+          <t>20250719-205203</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4666,10 +4666,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4688,56 +4688,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="C4" t="n">
-        <v>195.2400736808777</v>
+        <v>688.7270946502686</v>
       </c>
       <c r="D4" t="n">
-        <v>5.989999771118164</v>
+        <v>6.099999904632568</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1301223449409007</v>
+        <v>0.128711777212827</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6750008463859558</v>
+        <v>0.8111933469772339</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6750008463859558</v>
+        <v>0.8111933469772339</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6712369918823242</v>
+        <v>0.8094791173934937</v>
       </c>
       <c r="I4" t="n">
-        <v>0.662190318107605</v>
+        <v>0.798062801361084</v>
       </c>
       <c r="J4" t="n">
-        <v>0.063183881342411</v>
+        <v>0.0644122436642646</v>
       </c>
       <c r="K4" t="n">
-        <v>108.0177447795868</v>
+        <v>106.5697116851807</v>
       </c>
       <c r="L4" t="n">
-        <v>3.49650764465332</v>
+        <v>3.641177654266357</v>
       </c>
       <c r="M4" t="n">
-        <v>28.3343939781189</v>
+        <v>28.75566720962524</v>
       </c>
       <c r="N4" t="n">
-        <v>25.37074780464172</v>
+        <v>25.50874423980713</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0116550254821777</v>
+        <v>0.0121372588475545</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0944479799270629</v>
+        <v>0.0958522240320841</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0845691593488057</v>
+        <v>0.08502914746602371</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-085005</t>
+          <t>20250719-210558</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4762,22 +4762,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4787,10 +4787,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4809,56 +4809,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="C5" t="n">
-        <v>194.4984135627746</v>
+        <v>578.5288753509521</v>
       </c>
       <c r="D5" t="n">
-        <v>5.619999885559082</v>
+        <v>5.889999866485596</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1299917238454023</v>
+        <v>0.1304111625803144</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7427555918693542</v>
+        <v>0.797992467880249</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7427555918693542</v>
+        <v>0.797992467880249</v>
       </c>
       <c r="H5" t="n">
-        <v>0.740254282951355</v>
+        <v>0.7944998145103455</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7430851459503174</v>
+        <v>0.7996867895126343</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0623923875391483</v>
+        <v>0.06306906044483181</v>
       </c>
       <c r="K5" t="n">
-        <v>106.0243797302246</v>
+        <v>87.29254364967346</v>
       </c>
       <c r="L5" t="n">
-        <v>3.458729028701782</v>
+        <v>3.481269359588623</v>
       </c>
       <c r="M5" t="n">
-        <v>28.26812171936035</v>
+        <v>28.78709697723389</v>
       </c>
       <c r="N5" t="n">
-        <v>26.40891170501709</v>
+        <v>25.1310350894928</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0115290967623392</v>
+        <v>0.0116042311986287</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0942270723978678</v>
+        <v>0.0959569899241129</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0880297056833903</v>
+        <v>0.08377011696497599</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-085708</t>
+          <t>20250719-212115</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4908,10 +4908,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4930,56 +4930,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C6" t="n">
-        <v>196.0285289287567</v>
+        <v>834.4294731616974</v>
       </c>
       <c r="D6" t="n">
-        <v>5.989999771118164</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1307259711126486</v>
+        <v>0.1290684728217976</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7132998108863831</v>
+        <v>0.8047935366630554</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7132998108863831</v>
+        <v>0.8047935366630554</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7090631723403931</v>
+        <v>0.801723301410675</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6994566917419434</v>
+        <v>0.7935315370559692</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0613941885530948</v>
+        <v>0.06282062828540801</v>
       </c>
       <c r="K6" t="n">
-        <v>85.02652812004089</v>
+        <v>108.4669222831726</v>
       </c>
       <c r="L6" t="n">
-        <v>3.519271612167358</v>
+        <v>3.498299121856689</v>
       </c>
       <c r="M6" t="n">
-        <v>28.02124190330505</v>
+        <v>28.68978261947632</v>
       </c>
       <c r="N6" t="n">
-        <v>26.207594871521</v>
+        <v>26.51096081733704</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0117309053738911</v>
+        <v>0.0116609970728556</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0934041396776835</v>
+        <v>0.0956326087315877</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0873586495717366</v>
+        <v>0.0883698693911234</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-090349</t>
+          <t>20250719-213443</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5004,22 +5004,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5029,10 +5029,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5217,56 +5217,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C2" t="n">
-        <v>175.6922769546509</v>
+        <v>615.1999402046204</v>
       </c>
       <c r="D2" t="n">
-        <v>4.230000019073486</v>
+        <v>4.510000228881836</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1182792112231254</v>
+        <v>0.1192569832007089</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5993430018424988</v>
+        <v>0.7735927104949951</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5993430018424988</v>
+        <v>0.7735927104949951</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5988408923149109</v>
+        <v>0.772036075592041</v>
       </c>
       <c r="I2" t="n">
-        <v>0.596382737159729</v>
+        <v>0.7678287029266357</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0543970540165901</v>
+        <v>0.0525138564407825</v>
       </c>
       <c r="K2" t="n">
-        <v>68.33969402313232</v>
+        <v>69.25054049491882</v>
       </c>
       <c r="L2" t="n">
-        <v>3.085303544998169</v>
+        <v>2.983519077301025</v>
       </c>
       <c r="M2" t="n">
-        <v>24.9108624458313</v>
+        <v>25.90471625328064</v>
       </c>
       <c r="N2" t="n">
-        <v>23.86486649513245</v>
+        <v>26.75081515312195</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0102843451499938</v>
+        <v>0.0099450635910034</v>
       </c>
       <c r="P2" t="n">
-        <v>0.08303620815277089</v>
+        <v>0.08634905417760209</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.07954955498377481</v>
+        <v>0.08916938384373981</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-104342</t>
+          <t>20250720-010041</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5291,22 +5291,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5316,10 +5316,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5338,56 +5338,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C3" t="n">
-        <v>176.7080211639404</v>
+        <v>755.0279121398926</v>
       </c>
       <c r="D3" t="n">
-        <v>3.950000047683716</v>
+        <v>4.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1180167558292547</v>
+        <v>0.1175663990101643</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5375024676322937</v>
+        <v>0.770175039768219</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5375024676322937</v>
+        <v>0.770175039768219</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5350106954574585</v>
+        <v>0.7682087421417236</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5203106999397278</v>
+        <v>0.7615104913711548</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0639684051275253</v>
+        <v>0.0556784570217132</v>
       </c>
       <c r="K3" t="n">
-        <v>88.45860242843628</v>
+        <v>92.58655452728271</v>
       </c>
       <c r="L3" t="n">
-        <v>3.389271974563598</v>
+        <v>3.465158462524414</v>
       </c>
       <c r="M3" t="n">
-        <v>24.61322975158692</v>
+        <v>25.67127060890198</v>
       </c>
       <c r="N3" t="n">
-        <v>24.95320391654968</v>
+        <v>25.84345221519471</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0112975732485453</v>
+        <v>0.0115505282084147</v>
       </c>
       <c r="P3" t="n">
-        <v>0.08204409917195631</v>
+        <v>0.0855709020296732</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0831773463884989</v>
+        <v>0.0861448407173156</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-104940</t>
+          <t>20250720-011345</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5412,22 +5412,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5437,10 +5437,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5459,56 +5459,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C4" t="n">
-        <v>176.3900027275085</v>
+        <v>796.8959426879883</v>
       </c>
       <c r="D4" t="n">
-        <v>4.239999771118164</v>
+        <v>4.599999904632568</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1185844025264183</v>
+        <v>0.1211181381910011</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5008091926574707</v>
+        <v>0.7928229570388794</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5008091926574707</v>
+        <v>0.7928229570388794</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4990527331829071</v>
+        <v>0.7910665273666382</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2148119509220123</v>
+        <v>0.7879475355148315</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0555048957467079</v>
+        <v>0.0542123354971408</v>
       </c>
       <c r="K4" t="n">
-        <v>69.25690698623657</v>
+        <v>89.28753018379211</v>
       </c>
       <c r="L4" t="n">
-        <v>3.080169677734375</v>
+        <v>3.095440864562988</v>
       </c>
       <c r="M4" t="n">
-        <v>23.99061107635498</v>
+        <v>25.90835499763489</v>
       </c>
       <c r="N4" t="n">
-        <v>24.07087469100952</v>
+        <v>25.27476596832276</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0102672322591145</v>
+        <v>0.0103181362152099</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0799687035878499</v>
+        <v>0.08636118332544961</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0802362489700317</v>
+        <v>0.0842492198944091</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-105540</t>
+          <t>20250720-012952</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5533,22 +5533,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5558,10 +5558,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5580,56 +5580,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="C5" t="n">
-        <v>173.3571939468384</v>
+        <v>915.6632585525512</v>
       </c>
       <c r="D5" t="n">
-        <v>4.179999828338623</v>
+        <v>4.610000133514404</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1161761668821175</v>
+        <v>0.1180283308905713</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5569148659706116</v>
+        <v>0.7767126560211182</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5569148659706116</v>
+        <v>0.7767126560211182</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5551388263702393</v>
+        <v>0.7750888466835022</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5532882213592529</v>
+        <v>0.7772117853164673</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06421204656362529</v>
+        <v>0.056027565151453</v>
       </c>
       <c r="K5" t="n">
-        <v>88.81742072105408</v>
+        <v>90.69663238525391</v>
       </c>
       <c r="L5" t="n">
-        <v>3.35510802268982</v>
+        <v>3.160968542098999</v>
       </c>
       <c r="M5" t="n">
-        <v>24.73333668708801</v>
+        <v>25.57798719406128</v>
       </c>
       <c r="N5" t="n">
-        <v>25.31392478942871</v>
+        <v>26.75269412994385</v>
       </c>
       <c r="O5" t="n">
-        <v>0.011183693408966</v>
+        <v>0.0105365618069966</v>
       </c>
       <c r="P5" t="n">
-        <v>0.08244445562362671</v>
+        <v>0.0852599573135376</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0843797492980957</v>
+        <v>0.08917564709981279</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-110140</t>
+          <t>20250720-014616</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5679,10 +5679,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5701,56 +5701,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>173.9564428329468</v>
+        <v>644.2654993534088</v>
       </c>
       <c r="D6" t="n">
-        <v>4.070000171661377</v>
+        <v>4.590000152587891</v>
       </c>
       <c r="E6" t="n">
-        <v>0.116465692097942</v>
+        <v>0.1164011827980478</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5712053775787354</v>
+        <v>0.7783717513084412</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5712053775787354</v>
+        <v>0.7783717513084412</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5695866942405701</v>
+        <v>0.774920642375946</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5085933804512024</v>
+        <v>0.7726485133171082</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0510218478739261</v>
+        <v>0.0520935952663421</v>
       </c>
       <c r="K6" t="n">
-        <v>67.36670970916748</v>
+        <v>90.34464240074158</v>
       </c>
       <c r="L6" t="n">
-        <v>2.940032720565796</v>
+        <v>2.984776496887207</v>
       </c>
       <c r="M6" t="n">
-        <v>24.84170079231263</v>
+        <v>26.04304337501526</v>
       </c>
       <c r="N6" t="n">
-        <v>25.41626763343811</v>
+        <v>26.26273989677429</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009800109068552601</v>
+        <v>0.009949254989624</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0828056693077087</v>
+        <v>0.08681014458338419</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.08472089211146031</v>
+        <v>0.08754246632258091</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-110758</t>
+          <t>20250720-020442</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5775,22 +5775,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5800,10 +5800,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>

--- a/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-medium_voc_otx_cut.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-medium_voc_otx_cut.xlsx
@@ -594,53 +594,53 @@
         <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>121.7937743663788</v>
+        <v>121.15469622612</v>
       </c>
       <c r="D2" t="n">
-        <v>2.920000076293945</v>
+        <v>2.950000047683716</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0575882781829152</v>
+        <v>0.0578455839838299</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8589034080505371</v>
+        <v>0.858769416809082</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8589034080505371</v>
+        <v>0.858769416809082</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8570287227630615</v>
+        <v>0.8569109439849854</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8548480868339539</v>
+        <v>0.8549285531044006</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0494686104357242</v>
+        <v>0.0485863983631134</v>
       </c>
       <c r="K2" t="n">
-        <v>117.694658279419</v>
+        <v>116.9302849769592</v>
       </c>
       <c r="L2" t="n">
-        <v>2.831365823745728</v>
+        <v>2.806740522384644</v>
       </c>
       <c r="M2" t="n">
-        <v>34.43973994255066</v>
+        <v>33.86705207824707</v>
       </c>
       <c r="N2" t="n">
-        <v>27.05940651893616</v>
+        <v>27.20229649543763</v>
       </c>
       <c r="O2" t="n">
-        <v>0.009437886079152399</v>
+        <v>0.0093558017412821</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1147991331418355</v>
+        <v>0.1128901735941569</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0901980217297871</v>
+        <v>0.09067432165145869</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250720-052515</t>
+          <t>20250723-161807</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -715,53 +715,53 @@
         <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>194.6314074993133</v>
+        <v>193.3858740329742</v>
       </c>
       <c r="D3" t="n">
-        <v>2.970000028610229</v>
+        <v>2.730000019073486</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0573837272822856</v>
+        <v>0.0579803032071693</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8664580583572388</v>
+        <v>0.8657938241958618</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8664580583572388</v>
+        <v>0.8657938241958618</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8648409247398376</v>
+        <v>0.8641839027404785</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8655320405960083</v>
+        <v>0.8646316528320312</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0486292466521263</v>
+        <v>0.0494921840727329</v>
       </c>
       <c r="K3" t="n">
-        <v>97.38388538360596</v>
+        <v>97.06499886512756</v>
       </c>
       <c r="L3" t="n">
-        <v>2.870413780212402</v>
+        <v>2.817177534103394</v>
       </c>
       <c r="M3" t="n">
-        <v>34.6543116569519</v>
+        <v>34.56844210624695</v>
       </c>
       <c r="N3" t="n">
-        <v>27.14556813240052</v>
+        <v>27.7597930431366</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0095680459340413</v>
+        <v>0.0093905917803446</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1155143721898396</v>
+        <v>0.1152281403541564</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.09048522710800171</v>
+        <v>0.0925326434771219</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250720-053120</t>
+          <t>20250723-162411</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -836,53 +836,53 @@
         <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>227.1069238185882</v>
+        <v>222.8335783481598</v>
       </c>
       <c r="D4" t="n">
-        <v>3.019999980926514</v>
+        <v>2.849999904632568</v>
       </c>
       <c r="E4" t="n">
-        <v>0.057619768988203</v>
+        <v>0.0573110628735135</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8670738339424133</v>
+        <v>0.867113471031189</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8670738339424133</v>
+        <v>0.867113471031189</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8653272390365601</v>
+        <v>0.8653149604797363</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8652161955833435</v>
+        <v>0.8664728403091431</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0490317530930042</v>
+        <v>0.0599944181740284</v>
       </c>
       <c r="K4" t="n">
-        <v>98.21344399452209</v>
+        <v>135.8326153755188</v>
       </c>
       <c r="L4" t="n">
-        <v>2.844554901123047</v>
+        <v>4.201511859893799</v>
       </c>
       <c r="M4" t="n">
-        <v>35.51193261146545</v>
+        <v>35.98273110389709</v>
       </c>
       <c r="N4" t="n">
-        <v>27.67986178398132</v>
+        <v>28.82787322998047</v>
       </c>
       <c r="O4" t="n">
-        <v>0.009481849670410099</v>
+        <v>0.0140050395329793</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1183731087048848</v>
+        <v>0.1199424370129903</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0922662059466044</v>
+        <v>0.09609291076660149</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250720-053839</t>
+          <t>20250723-163</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -957,53 +957,53 @@
         <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>187.218635559082</v>
+        <v>187.0493597984314</v>
       </c>
       <c r="D5" t="n">
-        <v>2.950000047683716</v>
+        <v>2.509999990463257</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0575863226232203</v>
+        <v>0.0574831061742522</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8691561222076416</v>
+        <v>0.8687979578971863</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8691561222076416</v>
+        <v>0.8687979578971863</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8684744238853455</v>
+        <v>0.8681492209434509</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8685203790664673</v>
+        <v>0.8681050539016724</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0481590740382671</v>
+        <v>0.0504213869571685</v>
       </c>
       <c r="K5" t="n">
-        <v>119.0388715267181</v>
+        <v>110.4107005596161</v>
       </c>
       <c r="L5" t="n">
-        <v>2.879686832427979</v>
+        <v>2.873281002044678</v>
       </c>
       <c r="M5" t="n">
-        <v>34.99031782150269</v>
+        <v>35.79689598083496</v>
       </c>
       <c r="N5" t="n">
-        <v>27.76391911506653</v>
+        <v>28.81239128112793</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0095989561080932</v>
+        <v>0.009577603340148899</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1166343927383422</v>
+        <v>0.1193229866027832</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0925463970502217</v>
+        <v>0.0960413042704264</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250720-054612</t>
+          <t>20250723-164407</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1078,53 +1078,53 @@
         <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>154.6058716773987</v>
+        <v>155.6076290607452</v>
       </c>
       <c r="D6" t="n">
-        <v>3.450000047683716</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0578741418818632</v>
+        <v>0.0579440957970089</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8706749677658081</v>
+        <v>0.8702484369277954</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8706749677658081</v>
+        <v>0.8702484369277954</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8690341114997864</v>
+        <v>0.8684720993041992</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8683939576148987</v>
+        <v>0.8678446412086487</v>
       </c>
       <c r="J6" t="n">
-        <v>0.050305601209402</v>
+        <v>0.0498376786708831</v>
       </c>
       <c r="K6" t="n">
-        <v>119.278862953186</v>
+        <v>137.0838673114777</v>
       </c>
       <c r="L6" t="n">
-        <v>2.91360092163086</v>
+        <v>2.882683515548706</v>
       </c>
       <c r="M6" t="n">
-        <v>34.81811738014221</v>
+        <v>36.94887685775757</v>
       </c>
       <c r="N6" t="n">
-        <v>28.27347469329834</v>
+        <v>29.61801362037659</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0097120030721028</v>
+        <v>0.009608945051829</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1160603912671407</v>
+        <v>0.1231629228591918</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0942449156443278</v>
+        <v>0.0987267120679219</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250720-055325</t>
+          <t>20250723-165135</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1362,56 +1362,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="C2" t="n">
-        <v>1040.669723272324</v>
+        <v>1493.245532274246</v>
       </c>
       <c r="D2" t="n">
-        <v>3.589999914169312</v>
+        <v>3.430000066757202</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1592870262162438</v>
+        <v>0.1593044483590693</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4335594773292541</v>
+        <v>0.4497013390064239</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4335594773292541</v>
+        <v>0.4497013390064239</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4325537383556366</v>
+        <v>0.4475526511669159</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4118233323097229</v>
+        <v>0.3973183035850525</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0785726308822631</v>
+        <v>0.0824034512042999</v>
       </c>
       <c r="K2" t="n">
-        <v>280.1349849700928</v>
+        <v>279.2029058933258</v>
       </c>
       <c r="L2" t="n">
-        <v>4.292927026748657</v>
+        <v>4.363957643508911</v>
       </c>
       <c r="M2" t="n">
-        <v>27.16703820228577</v>
+        <v>27.73007035255432</v>
       </c>
       <c r="N2" t="n">
-        <v>29.57709670066833</v>
+        <v>29.16114068031311</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0143097567558288</v>
+        <v>0.014546525478363</v>
       </c>
       <c r="P2" t="n">
-        <v>0.09055679400761921</v>
+        <v>0.0924335678418477</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0985903223355611</v>
+        <v>0.0972038022677103</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-094348</t>
+          <t>20250721-154251</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1483,56 +1483,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>994.8900792598724</v>
+        <v>1052.663123607635</v>
       </c>
       <c r="D3" t="n">
-        <v>3.380000114440918</v>
+        <v>3.549999952316284</v>
       </c>
       <c r="E3" t="n">
-        <v>0.158396285825542</v>
+        <v>0.1589830207117533</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4611483812332153</v>
+        <v>0.4226632714271545</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4611483812332153</v>
+        <v>0.4226632714271545</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4577746987342834</v>
+        <v>0.4197779297828674</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4215841591358185</v>
+        <v>0.4024790525436401</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0766185745596885</v>
+        <v>0.0759985074400901</v>
       </c>
       <c r="K3" t="n">
-        <v>280.218624830246</v>
+        <v>280.5386438369751</v>
       </c>
       <c r="L3" t="n">
-        <v>4.499752759933472</v>
+        <v>4.479471921920776</v>
       </c>
       <c r="M3" t="n">
-        <v>26.80859589576721</v>
+        <v>26.99921536445618</v>
       </c>
       <c r="N3" t="n">
-        <v>29.64814186096192</v>
+        <v>29.52854013442993</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0149991758664449</v>
+        <v>0.0149315730730692</v>
       </c>
       <c r="P3" t="n">
-        <v>0.089361986319224</v>
+        <v>0.0899973845481872</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0988271395365397</v>
+        <v>0.0984284671147664</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250718-100746</t>
+          <t>20250721-161422</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1604,56 +1604,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C4" t="n">
-        <v>1182.078561067581</v>
+        <v>808.1239950656891</v>
       </c>
       <c r="D4" t="n">
-        <v>3.589999914169312</v>
+        <v>3.539999961853028</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1600712727416645</v>
+        <v>0.1591183811426162</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4409859180450439</v>
+        <v>0.4223624765872955</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4409859180450439</v>
+        <v>0.4223624765872955</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4374566674232483</v>
+        <v>0.4192744195461273</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4218841791152954</v>
+        <v>0.3280270099639892</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0774475261569023</v>
+        <v>0.0819309130311012</v>
       </c>
       <c r="K4" t="n">
-        <v>278.1540446281433</v>
+        <v>278.6050281524658</v>
       </c>
       <c r="L4" t="n">
-        <v>4.21699857711792</v>
+        <v>4.446515798568726</v>
       </c>
       <c r="M4" t="n">
-        <v>27.28056406974792</v>
+        <v>27.00691866874695</v>
       </c>
       <c r="N4" t="n">
-        <v>30.48619985580444</v>
+        <v>28.94018769264221</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0140566619237263</v>
+        <v>0.0148217193285624</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0909352135658264</v>
+        <v>0.0900230622291565</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1016206661860148</v>
+        <v>0.0964672923088073</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250718-103059</t>
+          <t>20250721-163852</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1725,56 +1725,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C5" t="n">
-        <v>872.3858640193939</v>
+        <v>1089.100641012192</v>
       </c>
       <c r="D5" t="n">
-        <v>3.650000095367432</v>
+        <v>3.599999904632568</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1618231566001971</v>
+        <v>0.1594902040039906</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4513498246669769</v>
+        <v>0.4085463285446167</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4513498246669769</v>
+        <v>0.4085463285446167</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4452738165855407</v>
+        <v>0.4055010676383972</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4067710936069488</v>
+        <v>0.3966937065124511</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0791566595435142</v>
+        <v>0.0791231915354728</v>
       </c>
       <c r="K5" t="n">
-        <v>278.1097288131714</v>
+        <v>278.9341852664948</v>
       </c>
       <c r="L5" t="n">
-        <v>4.294839859008789</v>
+        <v>4.314991474151611</v>
       </c>
       <c r="M5" t="n">
-        <v>28.07421898841858</v>
+        <v>27.59826731681824</v>
       </c>
       <c r="N5" t="n">
-        <v>29.225266456604</v>
+        <v>30.30591750144958</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0143161328633626</v>
+        <v>0.0143833049138387</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0935807299613952</v>
+        <v>0.0919942243893941</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0974175548553466</v>
+        <v>0.1010197250048319</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250718-105717</t>
+          <t>20250721-165915</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1846,56 +1846,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="C6" t="n">
-        <v>1506.020116090774</v>
+        <v>1175.850949764252</v>
       </c>
       <c r="D6" t="n">
-        <v>3.599999904632568</v>
+        <v>3.420000076293945</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1588170593275742</v>
+        <v>0.1591300442814826</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4874013066291809</v>
+        <v>0.44145467877388</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4874013066291809</v>
+        <v>0.44145467877388</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4866408407688141</v>
+        <v>0.438190758228302</v>
       </c>
       <c r="I6" t="n">
-        <v>0.456002414226532</v>
+        <v>0.3851353228092193</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0744615197181701</v>
+        <v>0.0735419988632202</v>
       </c>
       <c r="K6" t="n">
-        <v>278.7151334285736</v>
+        <v>279.0805027484894</v>
       </c>
       <c r="L6" t="n">
-        <v>4.096726655960083</v>
+        <v>4.399525165557861</v>
       </c>
       <c r="M6" t="n">
-        <v>27.51107168197632</v>
+        <v>27.10918521881104</v>
       </c>
       <c r="N6" t="n">
-        <v>29.54946756362915</v>
+        <v>30.08203148841858</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0136557555198669</v>
+        <v>0.0146650838851928</v>
       </c>
       <c r="P6" t="n">
-        <v>0.09170357227325431</v>
+        <v>0.0903639507293701</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0984982252120971</v>
+        <v>0.1002734382947286</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250718-111825</t>
+          <t>20250721-172422</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2136,53 +2136,53 @@
         <v>63</v>
       </c>
       <c r="C2" t="n">
-        <v>983.8640806674956</v>
+        <v>986.091599225998</v>
       </c>
       <c r="D2" t="n">
-        <v>2.339999914169312</v>
+        <v>2.390000104904175</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1370322586052001</v>
+        <v>0.1383856468730502</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4407634735107422</v>
+        <v>0.4519139230251312</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4407634735107422</v>
+        <v>0.4519139230251312</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4418756067752838</v>
+        <v>0.4491567015647888</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1708790361881256</v>
+        <v>0.1923235058784485</v>
       </c>
       <c r="J2" t="n">
-        <v>0.069662258028984</v>
+        <v>0.0663177073001861</v>
       </c>
       <c r="K2" t="n">
-        <v>227.957426071167</v>
+        <v>226.6001055240631</v>
       </c>
       <c r="L2" t="n">
-        <v>4.049444437026978</v>
+        <v>3.571749687194824</v>
       </c>
       <c r="M2" t="n">
-        <v>45.03544473648071</v>
+        <v>44.85155534744263</v>
       </c>
       <c r="N2" t="n">
-        <v>48.16569018363953</v>
+        <v>49.56750535964966</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0134981481234232</v>
+        <v>0.0119058322906494</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1501181491216023</v>
+        <v>0.1495051844914754</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1605523006121317</v>
+        <v>0.1652250178654988</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-154852</t>
+          <t>20250721-222603</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2254,56 +2254,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C3" t="n">
-        <v>1404.234761953354</v>
+        <v>1135.194409132004</v>
       </c>
       <c r="D3" t="n">
-        <v>2.609999895095825</v>
+        <v>2.380000114440918</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1370013981730073</v>
+        <v>0.137786106499907</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4653962850570678</v>
+        <v>0.4563488364219665</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4653962850570678</v>
+        <v>0.4563488364219665</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4664292335510254</v>
+        <v>0.4528275430202484</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1679614931344986</v>
+        <v>0.228900134563446</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0650599524378776</v>
+        <v>0.06539403647184371</v>
       </c>
       <c r="K3" t="n">
-        <v>226.4614882469177</v>
+        <v>226.0803253650665</v>
       </c>
       <c r="L3" t="n">
-        <v>3.633116960525513</v>
+        <v>3.655661582946777</v>
       </c>
       <c r="M3" t="n">
-        <v>45.14480781555176</v>
+        <v>44.60709476470947</v>
       </c>
       <c r="N3" t="n">
-        <v>50.83521151542664</v>
+        <v>49.93764019012451</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0121103898684183</v>
+        <v>0.0121855386098225</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1504826927185058</v>
+        <v>0.1486903158823649</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1694507050514221</v>
+        <v>0.1664588006337483</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250718-161136</t>
+          <t>20250721-224849</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -2375,56 +2375,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C4" t="n">
-        <v>1158.33188700676</v>
+        <v>1190.082921743393</v>
       </c>
       <c r="D4" t="n">
-        <v>2.380000114440918</v>
+        <v>2.619999885559082</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1382459126211501</v>
+        <v>0.1367536287803154</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4294037818908691</v>
+        <v>0.4359675049781799</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4294037818908691</v>
+        <v>0.4359675049781799</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4253938496112823</v>
+        <v>0.4354180097579956</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2248849272727966</v>
+        <v>0.2238468080759048</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0698926970362663</v>
+        <v>0.07156913727521889</v>
       </c>
       <c r="K4" t="n">
-        <v>227.8195104598999</v>
+        <v>228.4512958526612</v>
       </c>
       <c r="L4" t="n">
-        <v>3.762341976165772</v>
+        <v>3.852325677871704</v>
       </c>
       <c r="M4" t="n">
-        <v>45.05702161788941</v>
+        <v>45.57410645484924</v>
       </c>
       <c r="N4" t="n">
-        <v>49.30502653121948</v>
+        <v>50.28592872619629</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0125411399205525</v>
+        <v>0.0128410855929056</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1501900720596313</v>
+        <v>0.1519136881828308</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1643500884373982</v>
+        <v>0.1676197624206543</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250718-164122</t>
+          <t>20250721-231404</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2499,53 +2499,53 @@
         <v>61</v>
       </c>
       <c r="C5" t="n">
-        <v>954.6415822505952</v>
+        <v>965.0969531536102</v>
       </c>
       <c r="D5" t="n">
-        <v>2.440000057220459</v>
+        <v>2.390000104904175</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1378583524559364</v>
+        <v>0.1390991320864098</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4262373745441437</v>
+        <v>0.4278683066368103</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4262373745441437</v>
+        <v>0.4278683066368103</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4258880615234375</v>
+        <v>0.4268673360347748</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0404067374765872</v>
+        <v>0.1959102898836136</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0723888278007507</v>
+        <v>0.0718758106231689</v>
       </c>
       <c r="K5" t="n">
-        <v>227.6127681732178</v>
+        <v>227.0482940673828</v>
       </c>
       <c r="L5" t="n">
-        <v>3.868197679519653</v>
+        <v>4.191751480102539</v>
       </c>
       <c r="M5" t="n">
-        <v>45.18062734603882</v>
+        <v>43.70085287094116</v>
       </c>
       <c r="N5" t="n">
-        <v>48.56514286994934</v>
+        <v>49.9563992023468</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0128939922650655</v>
+        <v>0.0139725049336751</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1506020911534627</v>
+        <v>0.1456695095698038</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1618838095664978</v>
+        <v>0.1665213306744893</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250718-170701</t>
+          <t>20250721-234018</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2617,56 +2617,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C6" t="n">
-        <v>808.9806344509125</v>
+        <v>944.7997422218324</v>
       </c>
       <c r="D6" t="n">
-        <v>2.380000114440918</v>
+        <v>2.490000009536743</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1370629413196673</v>
+        <v>0.1360889040544384</v>
       </c>
       <c r="F6" t="n">
-        <v>0.343228131532669</v>
+        <v>0.4156281948089599</v>
       </c>
       <c r="G6" t="n">
-        <v>0.343228131532669</v>
+        <v>0.4156281948089599</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3435681760311126</v>
+        <v>0.415305495262146</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1790367364883422</v>
+        <v>0.2217652201652526</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06616265326738351</v>
+        <v>0.06895310431718819</v>
       </c>
       <c r="K6" t="n">
-        <v>227.2804524898529</v>
+        <v>227.8886036872864</v>
       </c>
       <c r="L6" t="n">
-        <v>3.916424751281737</v>
+        <v>3.75075101852417</v>
       </c>
       <c r="M6" t="n">
-        <v>44.7244553565979</v>
+        <v>44.73574852943421</v>
       </c>
       <c r="N6" t="n">
-        <v>51.17310166358948</v>
+        <v>49.46805238723755</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0130547491709391</v>
+        <v>0.0125025033950805</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1490815178553263</v>
+        <v>0.1491191617647806</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1705770055452982</v>
+        <v>0.1648935079574585</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250718-172937</t>
+          <t>20250722-000242</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2904,56 +2904,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>2264.355836868286</v>
+        <v>673.8432593345642</v>
       </c>
       <c r="D2" t="n">
-        <v>9.439999580383301</v>
+        <v>9.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3342647042238351</v>
+        <v>0.3331097568336286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.391095757484436</v>
+        <v>0.1539063304662704</v>
       </c>
       <c r="G2" t="n">
-        <v>0.391095757484436</v>
+        <v>0.1539063304662704</v>
       </c>
       <c r="H2" t="n">
-        <v>0.392266035079956</v>
+        <v>0.1530700176954269</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0747148990631103</v>
+        <v>0.0645257085561752</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1192799359560012</v>
+        <v>0.1120283529162406</v>
       </c>
       <c r="K2" t="n">
-        <v>1842.692344427109</v>
+        <v>1846.059047937393</v>
       </c>
       <c r="L2" t="n">
-        <v>6.653113126754761</v>
+        <v>6.525974750518799</v>
       </c>
       <c r="M2" t="n">
-        <v>47.08949375152588</v>
+        <v>47.19955897331238</v>
       </c>
       <c r="N2" t="n">
-        <v>50.8669228553772</v>
+        <v>50.77403950691223</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0221770437558492</v>
+        <v>0.0217532491683959</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1569649791717529</v>
+        <v>0.1573318632443746</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.169556409517924</v>
+        <v>0.1692467983563741</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-235203</t>
+          <t>20250722-080443</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3025,56 +3025,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="C3" t="n">
-        <v>2422.346768140793</v>
+        <v>3613.948223114014</v>
       </c>
       <c r="D3" t="n">
-        <v>9.449999809265137</v>
+        <v>9.439999580383301</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3334670650287413</v>
+        <v>0.3343214893116141</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3838217556476593</v>
+        <v>0.3765660524368286</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3838217556476593</v>
+        <v>0.3765660524368286</v>
       </c>
       <c r="H3" t="n">
-        <v>0.383714348077774</v>
+        <v>0.3768292665481567</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1070767939090728</v>
+        <v>0.0450519248843193</v>
       </c>
       <c r="J3" t="n">
-        <v>0.115086019039154</v>
+        <v>0.1136587560176849</v>
       </c>
       <c r="K3" t="n">
-        <v>1842.184654712677</v>
+        <v>1824.183166265488</v>
       </c>
       <c r="L3" t="n">
-        <v>6.497223138809204</v>
+        <v>6.415083169937134</v>
       </c>
       <c r="M3" t="n">
-        <v>47.6969256401062</v>
+        <v>46.69346523284912</v>
       </c>
       <c r="N3" t="n">
-        <v>50.21492433547974</v>
+        <v>51.41683769226074</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0216574104626973</v>
+        <v>0.0213836105664571</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1589897521336873</v>
+        <v>0.155644884109497</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1673830811182657</v>
+        <v>0.1713894589742024</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250719-010339</t>
+          <t>20250722-084951</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3146,56 +3146,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C4" t="n">
-        <v>2732.963873147964</v>
+        <v>2597.445121526718</v>
       </c>
       <c r="D4" t="n">
-        <v>9.5</v>
+        <v>9.449999809265137</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3343731746077537</v>
+        <v>0.3343988441322979</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3699622750282287</v>
+        <v>0.3888525366783142</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3699622750282287</v>
+        <v>0.3888525366783142</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3692367374897003</v>
+        <v>0.3886458277702331</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0737020000815391</v>
+        <v>0.0694458931684494</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1200625598430633</v>
+        <v>0.1142069995403289</v>
       </c>
       <c r="K4" t="n">
-        <v>1828.769851922989</v>
+        <v>1829.430955886841</v>
       </c>
       <c r="L4" t="n">
-        <v>6.714082717895508</v>
+        <v>6.203036546707153</v>
       </c>
       <c r="M4" t="n">
-        <v>47.23690843582153</v>
+        <v>47.28663897514343</v>
       </c>
       <c r="N4" t="n">
-        <v>50.21334338188171</v>
+        <v>50.85078144073486</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0223802757263183</v>
+        <v>0.0206767884890238</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1574563614527384</v>
+        <v>0.1576221299171447</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.167377811272939</v>
+        <v>0.1695026048024495</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250719-021752</t>
+          <t>20250722-102339</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3267,56 +3267,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C5" t="n">
-        <v>2056.612390518188</v>
+        <v>2174.41771697998</v>
       </c>
       <c r="D5" t="n">
-        <v>9.449999809265137</v>
+        <v>9.5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3335180694858233</v>
+        <v>0.3358775963858952</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3458226919174194</v>
+        <v>0.3309002518653869</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3458226919174194</v>
+        <v>0.3309002518653869</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3453357219696045</v>
+        <v>0.331129640340805</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0411288067698478</v>
+        <v>0.0674014165997505</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1172753423452377</v>
+        <v>0.1190326213836669</v>
       </c>
       <c r="K5" t="n">
-        <v>1847.139241695404</v>
+        <v>1828.437381744385</v>
       </c>
       <c r="L5" t="n">
-        <v>6.665947198867798</v>
+        <v>6.661808729171753</v>
       </c>
       <c r="M5" t="n">
-        <v>47.25520491600037</v>
+        <v>47.19480133056641</v>
       </c>
       <c r="N5" t="n">
-        <v>49.88571906089783</v>
+        <v>51.25130105018616</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0222198239962259</v>
+        <v>0.0222060290972391</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1575173497200012</v>
+        <v>0.1573160044352213</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1662857302029927</v>
+        <v>0.1708376701672871</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250719-033702</t>
+          <t>20250722-114034</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3388,56 +3388,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C6" t="n">
-        <v>2128.156713962555</v>
+        <v>1518.44741153717</v>
       </c>
       <c r="D6" t="n">
-        <v>9.449999809265137</v>
+        <v>9.529999732971191</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3337059487258234</v>
+        <v>0.3337442197582938</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3975653052330017</v>
+        <v>0.275970458984375</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3975653052330017</v>
+        <v>0.275970458984375</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3983821868896484</v>
+        <v>0.2759862840175628</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0843257904052734</v>
+        <v>0.0482160598039627</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1180085018277168</v>
+        <v>0.1150527670979499</v>
       </c>
       <c r="K6" t="n">
-        <v>1850.233253955841</v>
+        <v>1853.08593249321</v>
       </c>
       <c r="L6" t="n">
-        <v>6.627603530883789</v>
+        <v>6.47409462928772</v>
       </c>
       <c r="M6" t="n">
-        <v>46.32812643051148</v>
+        <v>45.98501896858215</v>
       </c>
       <c r="N6" t="n">
-        <v>50.80365109443665</v>
+        <v>50.17064309120178</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0220920117696126</v>
+        <v>0.021580315430959</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1544270881017049</v>
+        <v>0.1532833965619405</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1693455036481221</v>
+        <v>0.1672354769706726</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250719-044514</t>
+          <t>20250722-125026</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -3675,56 +3675,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>627.3350512981415</v>
+        <v>1125.667814254761</v>
       </c>
       <c r="D2" t="n">
-        <v>8.180000305175781</v>
+        <v>8.479999542236328</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2051198935067212</v>
+        <v>0.2040240097045898</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8353222608566284</v>
+        <v>0.8393394947052002</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8353222608566284</v>
+        <v>0.8393394947052002</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8335031270980835</v>
+        <v>0.8374847173690796</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8286496996879578</v>
+        <v>0.8289518356323242</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0851237773895263</v>
+        <v>0.08543740957975381</v>
       </c>
       <c r="K2" t="n">
-        <v>146.3149056434631</v>
+        <v>150.7823107242584</v>
       </c>
       <c r="L2" t="n">
-        <v>5.07035756111145</v>
+        <v>5.101834058761597</v>
       </c>
       <c r="M2" t="n">
-        <v>37.74934005737305</v>
+        <v>37.88319039344788</v>
       </c>
       <c r="N2" t="n">
-        <v>32.60042119026184</v>
+        <v>34.25642538070679</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0169011918703715</v>
+        <v>0.0170061135292053</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1258311335245768</v>
+        <v>0.1262773013114929</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1086680706342061</v>
+        <v>0.1141880846023559</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250719-142836</t>
+          <t>20250722-233915</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3796,56 +3796,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>604.0075459480286</v>
+        <v>579.3423969745636</v>
       </c>
       <c r="D3" t="n">
-        <v>8.319999694824219</v>
+        <v>8.279999732971191</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2047882372370133</v>
+        <v>0.204154440164566</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8269065618515015</v>
+        <v>0.8203190565109253</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8269065618515015</v>
+        <v>0.8203190565109253</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8234704732894897</v>
+        <v>0.8204610347747803</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8122720718383789</v>
+        <v>0.8234655261039734</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0843094140291214</v>
+        <v>0.0836313217878341</v>
       </c>
       <c r="K3" t="n">
-        <v>149.6965687274933</v>
+        <v>150.7558023929596</v>
       </c>
       <c r="L3" t="n">
-        <v>4.792565584182739</v>
+        <v>4.720711708068848</v>
       </c>
       <c r="M3" t="n">
-        <v>37.94105815887451</v>
+        <v>37.78942894935608</v>
       </c>
       <c r="N3" t="n">
-        <v>32.89355826377869</v>
+        <v>32.80958080291748</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0159752186139424</v>
+        <v>0.0157357056935628</v>
       </c>
       <c r="P3" t="n">
-        <v>0.126470193862915</v>
+        <v>0.1259647631645202</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1096451942125956</v>
+        <v>0.1093652693430582</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250719-144337</t>
+          <t>20250723-000241</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3917,56 +3917,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C4" t="n">
-        <v>887.8797624111176</v>
+        <v>778.2256734371185</v>
       </c>
       <c r="D4" t="n">
-        <v>8.380000114440918</v>
+        <v>8.329999923706055</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2048821250597635</v>
+        <v>0.2045432140721994</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8363301753997803</v>
+        <v>0.8351583480834961</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8363301753997803</v>
+        <v>0.8351583480834961</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8331738710403442</v>
+        <v>0.8337687849998474</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8250128030776978</v>
+        <v>0.8308853507041931</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0849953815340995</v>
+        <v>0.08503911644220349</v>
       </c>
       <c r="K4" t="n">
-        <v>145.9779160022736</v>
+        <v>148.463858127594</v>
       </c>
       <c r="L4" t="n">
-        <v>4.805693864822388</v>
+        <v>4.814059734344482</v>
       </c>
       <c r="M4" t="n">
-        <v>37.61803388595581</v>
+        <v>37.77534246444702</v>
       </c>
       <c r="N4" t="n">
-        <v>34.32653117179871</v>
+        <v>33.87355828285217</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0160189795494079</v>
+        <v>0.0160468657811482</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1253934462865193</v>
+        <v>0.1259178082148234</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1144217705726623</v>
+        <v>0.1129118609428405</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250719-145839</t>
+          <t>20250723-001659</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4038,56 +4038,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>537.0742132663727</v>
+        <v>668.5678019523621</v>
       </c>
       <c r="D5" t="n">
-        <v>8.359999656677246</v>
+        <v>8.279999732971191</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2049970607394757</v>
+        <v>0.2044462022082559</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8184016942977905</v>
+        <v>0.8310467004776001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8184016942977905</v>
+        <v>0.8310467004776001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8176806569099426</v>
+        <v>0.8309521675109863</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8095337748527527</v>
+        <v>0.784882128238678</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0843097940087318</v>
+        <v>0.08447430282831191</v>
       </c>
       <c r="K5" t="n">
-        <v>147.1088199615479</v>
+        <v>146.1678996086121</v>
       </c>
       <c r="L5" t="n">
-        <v>4.800802946090698</v>
+        <v>4.834947824478149</v>
       </c>
       <c r="M5" t="n">
-        <v>37.53899216651917</v>
+        <v>37.84948348999024</v>
       </c>
       <c r="N5" t="n">
-        <v>32.78650212287903</v>
+        <v>34.04466080665588</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0160026764869689</v>
+        <v>0.0161164927482605</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1251299738883972</v>
+        <v>0.1261649449666341</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1092883404095967</v>
+        <v>0.1134822026888529</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250719-151823</t>
+          <t>20250723-003435</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4159,56 +4159,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>666.9687857627869</v>
+        <v>822.2869772911072</v>
       </c>
       <c r="D6" t="n">
-        <v>8.340000152587891</v>
+        <v>8.529999732971191</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2045877765992592</v>
+        <v>0.2045707673662238</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8314225077629089</v>
+        <v>0.837373673915863</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8314225077629089</v>
+        <v>0.837373673915863</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8289631605148315</v>
+        <v>0.8364080190658569</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8206084966659546</v>
+        <v>0.8364056348800659</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08563999086618421</v>
+        <v>0.08426729589700691</v>
       </c>
       <c r="K6" t="n">
-        <v>147.273809671402</v>
+        <v>148.1186292171478</v>
       </c>
       <c r="L6" t="n">
-        <v>4.858999729156494</v>
+        <v>5.104294300079346</v>
       </c>
       <c r="M6" t="n">
-        <v>38.30568194389343</v>
+        <v>37.83700251579285</v>
       </c>
       <c r="N6" t="n">
-        <v>32.85431098937988</v>
+        <v>33.39628934860229</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0161966657638549</v>
+        <v>0.0170143143335978</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1276856064796447</v>
+        <v>0.1261233417193095</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1095143699645996</v>
+        <v>0.1113209644953409</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250719-153215</t>
+          <t>20250723-005039</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4446,56 +4446,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C2" t="n">
-        <v>679.1374168395996</v>
+        <v>956.1853427886964</v>
       </c>
       <c r="D2" t="n">
-        <v>5.940000057220459</v>
+        <v>5.989999771118164</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1304429299301571</v>
+        <v>0.1283585367294458</v>
       </c>
       <c r="F2" t="n">
-        <v>0.80670565366745</v>
+        <v>0.8120104670524597</v>
       </c>
       <c r="G2" t="n">
-        <v>0.80670565366745</v>
+        <v>0.8120104670524597</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8052331805229187</v>
+        <v>0.8106181621551514</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8051472902297974</v>
+        <v>0.8069137930870056</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0625762715935707</v>
+        <v>0.0586997345089912</v>
       </c>
       <c r="K2" t="n">
-        <v>106.254120349884</v>
+        <v>108.7316517829895</v>
       </c>
       <c r="L2" t="n">
-        <v>3.491467237472534</v>
+        <v>3.379822492599488</v>
       </c>
       <c r="M2" t="n">
-        <v>28.22064542770386</v>
+        <v>29.08442878723145</v>
       </c>
       <c r="N2" t="n">
-        <v>25.55138301849365</v>
+        <v>25.96821713447571</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0116382241249084</v>
+        <v>0.0112660749753316</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0940688180923461</v>
+        <v>0.0969480959574381</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0851712767283121</v>
+        <v>0.08656072378158559</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250719-203656</t>
+          <t>20250723-062048</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4567,56 +4567,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3" t="n">
-        <v>626.059424161911</v>
+        <v>678.534298658371</v>
       </c>
       <c r="D3" t="n">
-        <v>6.369999885559082</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1279324090906551</v>
+        <v>0.127462720417458</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8057955503463745</v>
+        <v>0.809342622756958</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8057955503463745</v>
+        <v>0.809342622756958</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8040726780891418</v>
+        <v>0.8082726001739502</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7995801568031311</v>
+        <v>0.7950782179832458</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0635520666837692</v>
+        <v>0.0646351724863052</v>
       </c>
       <c r="K3" t="n">
-        <v>86.0214900970459</v>
+        <v>107.9178183078766</v>
       </c>
       <c r="L3" t="n">
-        <v>3.516921758651733</v>
+        <v>3.660536766052246</v>
       </c>
       <c r="M3" t="n">
-        <v>28.65989637374878</v>
+        <v>28.93225359916687</v>
       </c>
       <c r="N3" t="n">
-        <v>27.43337202072144</v>
+        <v>26.74170303344727</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0117230725288391</v>
+        <v>0.0122017892201741</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0955329879124959</v>
+        <v>0.0964408453305562</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.09144457340240469</v>
+        <v>0.08913901011149079</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250719-205203</t>
+          <t>20250723-064035</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4688,56 +4688,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C4" t="n">
-        <v>688.7270946502686</v>
+        <v>1031.827417612076</v>
       </c>
       <c r="D4" t="n">
-        <v>6.099999904632568</v>
+        <v>6.309999942779541</v>
       </c>
       <c r="E4" t="n">
-        <v>0.128711777212827</v>
+        <v>0.1284091129899024</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8111933469772339</v>
+        <v>0.824041485786438</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8111933469772339</v>
+        <v>0.824041485786438</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8094791173934937</v>
+        <v>0.8208564519882202</v>
       </c>
       <c r="I4" t="n">
-        <v>0.798062801361084</v>
+        <v>0.8104324340820312</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0644122436642646</v>
+        <v>0.0634117275476455</v>
       </c>
       <c r="K4" t="n">
-        <v>106.5697116851807</v>
+        <v>88.40886402130127</v>
       </c>
       <c r="L4" t="n">
-        <v>3.641177654266357</v>
+        <v>3.637199878692627</v>
       </c>
       <c r="M4" t="n">
-        <v>28.75566720962524</v>
+        <v>29.83090281486511</v>
       </c>
       <c r="N4" t="n">
-        <v>25.50874423980713</v>
+        <v>27.06719326972961</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0121372588475545</v>
+        <v>0.012123999595642</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0958522240320841</v>
+        <v>0.099436342716217</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.08502914746602371</v>
+        <v>0.09022397756576531</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250719-210558</t>
+          <t>20250723-065545</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4809,56 +4809,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>578.5288753509521</v>
+        <v>747.5575931072235</v>
       </c>
       <c r="D5" t="n">
-        <v>5.889999866485596</v>
+        <v>5.989999771118164</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1304111625803144</v>
+        <v>0.1295506846904754</v>
       </c>
       <c r="F5" t="n">
-        <v>0.797992467880249</v>
+        <v>0.8099796175956726</v>
       </c>
       <c r="G5" t="n">
-        <v>0.797992467880249</v>
+        <v>0.8099796175956726</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7944998145103455</v>
+        <v>0.806759238243103</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7996867895126343</v>
+        <v>0.8007880449295044</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06306906044483181</v>
+        <v>0.0657720565795898</v>
       </c>
       <c r="K5" t="n">
-        <v>87.29254364967346</v>
+        <v>88.71089625358582</v>
       </c>
       <c r="L5" t="n">
-        <v>3.481269359588623</v>
+        <v>3.690232038497925</v>
       </c>
       <c r="M5" t="n">
-        <v>28.78709697723389</v>
+        <v>28.82445788383484</v>
       </c>
       <c r="N5" t="n">
-        <v>25.1310350894928</v>
+        <v>27.01268124580384</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0116042311986287</v>
+        <v>0.0123007734616597</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0959569899241129</v>
+        <v>0.09608152627944939</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.08377011696497599</v>
+        <v>0.0900422708193461</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250719-212115</t>
+          <t>20250723-071610</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4930,56 +4930,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
-        <v>834.4294731616974</v>
+        <v>511.9082252979279</v>
       </c>
       <c r="D6" t="n">
-        <v>5.940000057220459</v>
+        <v>6.039999961853027</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1290684728217976</v>
+        <v>0.1287656132789218</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8047935366630554</v>
+        <v>0.7955504059791565</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8047935366630554</v>
+        <v>0.7955504059791565</v>
       </c>
       <c r="H6" t="n">
-        <v>0.801723301410675</v>
+        <v>0.7925529479980469</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7935315370559692</v>
+        <v>0.7885863184928894</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06282062828540801</v>
+        <v>0.065346784889698</v>
       </c>
       <c r="K6" t="n">
-        <v>108.4669222831726</v>
+        <v>87.05951142311096</v>
       </c>
       <c r="L6" t="n">
-        <v>3.498299121856689</v>
+        <v>3.570580005645752</v>
       </c>
       <c r="M6" t="n">
-        <v>28.68978261947632</v>
+        <v>29.7566556930542</v>
       </c>
       <c r="N6" t="n">
-        <v>26.51096081733704</v>
+        <v>27.0089750289917</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0116609970728556</v>
+        <v>0.0119019333521525</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0956326087315877</v>
+        <v>0.0991888523101806</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0883698693911234</v>
+        <v>0.0900299167633056</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250719-213443</t>
+          <t>20250723-073149</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5217,56 +5217,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" t="n">
-        <v>615.1999402046204</v>
+        <v>622.5463955402374</v>
       </c>
       <c r="D2" t="n">
-        <v>4.510000228881836</v>
+        <v>4.75</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1192569832007089</v>
+        <v>0.1170663797984952</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7735927104949951</v>
+        <v>0.7620850801467896</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7735927104949951</v>
+        <v>0.7620850801467896</v>
       </c>
       <c r="H2" t="n">
-        <v>0.772036075592041</v>
+        <v>0.7603987455368042</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7678287029266357</v>
+        <v>0.7590667009353638</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0525138564407825</v>
+        <v>0.0574709139764308</v>
       </c>
       <c r="K2" t="n">
-        <v>69.25054049491882</v>
+        <v>70.51968693733215</v>
       </c>
       <c r="L2" t="n">
-        <v>2.983519077301025</v>
+        <v>3.120778799057007</v>
       </c>
       <c r="M2" t="n">
-        <v>25.90471625328064</v>
+        <v>25.44145274162292</v>
       </c>
       <c r="N2" t="n">
-        <v>26.75081515312195</v>
+        <v>26.374272108078</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0099450635910034</v>
+        <v>0.0104025959968566</v>
       </c>
       <c r="P2" t="n">
-        <v>0.08634905417760209</v>
+        <v>0.0848048424720764</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.08916938384373981</v>
+        <v>0.08791424036025999</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250720-010041</t>
+          <t>20250723-114550</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5338,56 +5338,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="C3" t="n">
-        <v>755.0279121398926</v>
+        <v>570.2515463829041</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5</v>
+        <v>4.559999942779541</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1175663990101643</v>
+        <v>0.1177309575889791</v>
       </c>
       <c r="F3" t="n">
-        <v>0.770175039768219</v>
+        <v>0.7798407077789307</v>
       </c>
       <c r="G3" t="n">
-        <v>0.770175039768219</v>
+        <v>0.7798407077789307</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7682087421417236</v>
+        <v>0.7760111093521118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7615104913711548</v>
+        <v>0.7709584832191467</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0556784570217132</v>
+        <v>0.0542112998664379</v>
       </c>
       <c r="K3" t="n">
-        <v>92.58655452728271</v>
+        <v>89.33822870254517</v>
       </c>
       <c r="L3" t="n">
-        <v>3.465158462524414</v>
+        <v>3.282464504241944</v>
       </c>
       <c r="M3" t="n">
-        <v>25.67127060890198</v>
+        <v>26.06149625778198</v>
       </c>
       <c r="N3" t="n">
-        <v>25.84345221519471</v>
+        <v>26.9431586265564</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0115505282084147</v>
+        <v>0.0109415483474731</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0855709020296732</v>
+        <v>0.0868716541926066</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0861448407173156</v>
+        <v>0.0898105287551879</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250720-011345</t>
+          <t>20250723-115922</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5459,56 +5459,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>796.8959426879883</v>
+        <v>519.418790102005</v>
       </c>
       <c r="D4" t="n">
-        <v>4.599999904632568</v>
+        <v>4.650000095367432</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1211181381910011</v>
+        <v>0.1175946669751091</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7928229570388794</v>
+        <v>0.7705578804016113</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7928229570388794</v>
+        <v>0.7705578804016113</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7910665273666382</v>
+        <v>0.7679192423820496</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7879475355148315</v>
+        <v>0.766664445400238</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0542123354971408</v>
+        <v>0.0552327074110507</v>
       </c>
       <c r="K4" t="n">
-        <v>89.28753018379211</v>
+        <v>69.48490333557129</v>
       </c>
       <c r="L4" t="n">
-        <v>3.095440864562988</v>
+        <v>3.068166494369507</v>
       </c>
       <c r="M4" t="n">
-        <v>25.90835499763489</v>
+        <v>25.50561213493347</v>
       </c>
       <c r="N4" t="n">
-        <v>25.27476596832276</v>
+        <v>25.63734936714172</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0103181362152099</v>
+        <v>0.0102272216478983</v>
       </c>
       <c r="P4" t="n">
-        <v>0.08636118332544961</v>
+        <v>0.08501870711644489</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0842492198944091</v>
+        <v>0.08545783122380569</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250720-012952</t>
+          <t>20250723-121202</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5583,53 +5583,53 @@
         <v>68</v>
       </c>
       <c r="C5" t="n">
-        <v>915.6632585525512</v>
+        <v>903.2101850509644</v>
       </c>
       <c r="D5" t="n">
-        <v>4.610000133514404</v>
+        <v>4.699999809265137</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1180283308905713</v>
+        <v>0.1157882212496855</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7767126560211182</v>
+        <v>0.7902849912643433</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7767126560211182</v>
+        <v>0.7902849912643433</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7750888466835022</v>
+        <v>0.7881225943565369</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7772117853164673</v>
+        <v>0.7891114354133606</v>
       </c>
       <c r="J5" t="n">
-        <v>0.056027565151453</v>
+        <v>0.0527153760194778</v>
       </c>
       <c r="K5" t="n">
-        <v>90.69663238525391</v>
+        <v>68.21791005134583</v>
       </c>
       <c r="L5" t="n">
-        <v>3.160968542098999</v>
+        <v>3.055084466934204</v>
       </c>
       <c r="M5" t="n">
-        <v>25.57798719406128</v>
+        <v>25.54434013366699</v>
       </c>
       <c r="N5" t="n">
-        <v>26.75269412994385</v>
+        <v>26.0366005897522</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0105365618069966</v>
+        <v>0.0101836148897806</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0852599573135376</v>
+        <v>0.0851478004455566</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.08917564709981279</v>
+        <v>0.0867886686325073</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250720-014616</t>
+          <t>20250723-122350</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5704,53 +5704,53 @@
         <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>644.2654993534088</v>
+        <v>649.4330899715424</v>
       </c>
       <c r="D6" t="n">
-        <v>4.590000152587891</v>
+        <v>4.559999942779541</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1164011827980478</v>
+        <v>0.1180871911346912</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7783717513084412</v>
+        <v>0.7707736492156982</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7783717513084412</v>
+        <v>0.7707736492156982</v>
       </c>
       <c r="H6" t="n">
-        <v>0.774920642375946</v>
+        <v>0.7699505686759949</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7726485133171082</v>
+        <v>0.7597068548202515</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0520935952663421</v>
+        <v>0.0600771456956863</v>
       </c>
       <c r="K6" t="n">
-        <v>90.34464240074158</v>
+        <v>68.51251721382141</v>
       </c>
       <c r="L6" t="n">
-        <v>2.984776496887207</v>
+        <v>3.260861158370972</v>
       </c>
       <c r="M6" t="n">
-        <v>26.04304337501526</v>
+        <v>25.27405214309692</v>
       </c>
       <c r="N6" t="n">
-        <v>26.26273989677429</v>
+        <v>25.21843361854553</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009949254989624</v>
+        <v>0.0108695371945699</v>
       </c>
       <c r="P6" t="n">
-        <v>0.08681014458338419</v>
+        <v>0.0842468404769897</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.08754246632258091</v>
+        <v>0.0840614453951517</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250720-020442</t>
+          <t>20250723-124200</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
